--- a/EXCEL/class notes/day7 vlookup/Vlookup Basic.xlsx
+++ b/EXCEL/class notes/day7 vlookup/Vlookup Basic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day7 vlookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397DFA5E-077D-400F-85E5-4605E700AD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59346258-AE1C-4BC9-B734-2C3F1518E8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="824" firstSheet="2" activeTab="4" xr2:uid="{20B15D0C-CB86-4A05-82F5-505530312088}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="824" firstSheet="2" activeTab="8" xr2:uid="{20B15D0C-CB86-4A05-82F5-505530312088}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic Vlookup" sheetId="6" r:id="rId1"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" ref="C6:C11" ca="1" si="1">RANDBETWEEN(1,100)</f>
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
@@ -2068,16 +2068,46 @@
       <c r="I6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
+      <c r="J6" s="55" t="str">
+        <f>VLOOKUP(J$5,$A$2:$C$11,2,0)</f>
+        <v>Ram4</v>
+      </c>
+      <c r="K6" s="55" t="str">
+        <f t="shared" ref="K6:S7" si="2">VLOOKUP(K$5,$A$2:$C$11,2,0)</f>
+        <v>Ram7</v>
+      </c>
+      <c r="L6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram9</v>
+      </c>
+      <c r="M6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram2</v>
+      </c>
+      <c r="N6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram8</v>
+      </c>
+      <c r="O6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram3</v>
+      </c>
+      <c r="P6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram5</v>
+      </c>
+      <c r="Q6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram10</v>
+      </c>
+      <c r="R6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram6</v>
+      </c>
+      <c r="S6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Ram1</v>
+      </c>
     </row>
     <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17">
@@ -2097,16 +2127,46 @@
       <c r="I7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
+      <c r="J7" s="55">
+        <f>VLOOKUP(J$5,$A2:C$11,3,0)</f>
+        <v>10</v>
+      </c>
+      <c r="K7" s="55">
+        <f ca="1">VLOOKUP(K$5,$A2:D$11,3,0)</f>
+        <v>28</v>
+      </c>
+      <c r="L7" s="55">
+        <f ca="1">VLOOKUP(L$5,$A2:E$11,3,0)</f>
+        <v>55</v>
+      </c>
+      <c r="M7" s="55">
+        <f>VLOOKUP(M$5,$A2:F$11,3,0)</f>
+        <v>55</v>
+      </c>
+      <c r="N7" s="55">
+        <f ca="1">VLOOKUP(N$5,$A2:G$11,3,0)</f>
+        <v>42</v>
+      </c>
+      <c r="O7" s="55">
+        <f>VLOOKUP(O$5,$A2:H$11,3,0)</f>
+        <v>66</v>
+      </c>
+      <c r="P7" s="55">
+        <f ca="1">VLOOKUP(P$5,$A2:I$11,3,0)</f>
+        <v>33</v>
+      </c>
+      <c r="Q7" s="55">
+        <f ca="1">VLOOKUP(Q$5,$A2:J$11,3,0)</f>
+        <v>92</v>
+      </c>
+      <c r="R7" s="55">
+        <f>VLOOKUP(R$5,$A2:K$11,3,0)</f>
+        <v>97</v>
+      </c>
+      <c r="S7" s="55">
+        <f>VLOOKUP(S$5,$A2:L$11,3,0)</f>
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="17">
@@ -2117,7 +2177,7 @@
       </c>
       <c r="C8" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="E8" s="29"/>
       <c r="F8" s="29"/>
@@ -2134,7 +2194,7 @@
       </c>
       <c r="C9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
@@ -2151,7 +2211,7 @@
       </c>
       <c r="C10" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="29"/>
@@ -2168,7 +2228,7 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29"/>
@@ -2798,26 +2858,26 @@
       </c>
       <c r="F3" s="3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3">
         <v>97</v>
       </c>
       <c r="H3" s="3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="I3" s="69">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J3" s="3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="K3" s="4">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>67</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2885,7 +2945,7 @@
     <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="29">
         <f t="shared" ref="A10:A18" ca="1" si="0">HLOOKUP($C10,$A$1:$K$3,3,0)</f>
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="B10" s="29" t="str">
         <f t="shared" ref="B10:B18" si="1">HLOOKUP($C10,$A$1:$K$3,2,0)</f>
@@ -2903,11 +2963,11 @@
       </c>
       <c r="G10" s="55">
         <f t="shared" ref="G10:O10" ca="1" si="2">HLOOKUP(G$9,$A$1:$K$3,3,0)</f>
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="H10" s="55">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="I10" s="55">
         <f t="shared" si="2"/>
@@ -2915,7 +2975,7 @@
       </c>
       <c r="J10" s="55">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K10" s="55">
         <f t="shared" si="2"/>
@@ -2923,11 +2983,11 @@
       </c>
       <c r="L10" s="55">
         <f t="shared" ca="1" si="2"/>
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="M10" s="55">
         <f t="shared" ca="1" si="2"/>
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="N10" s="55">
         <f t="shared" si="2"/>
@@ -2945,7 +3005,7 @@
     <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="B11" s="29" t="str">
         <f t="shared" si="1"/>
@@ -3018,7 +3078,7 @@
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B13" s="29" t="str">
         <f t="shared" si="1"/>
@@ -3047,7 +3107,7 @@
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B15" s="29" t="str">
         <f t="shared" si="1"/>
@@ -3060,7 +3120,7 @@
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="B16" s="29" t="str">
         <f t="shared" si="1"/>
@@ -3276,19 +3336,19 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" ref="C6:C11" ca="1" si="5">RANDBETWEEN(1,100)</f>
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>C+</v>
+        <v>B</v>
       </c>
       <c r="E6" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>First class</v>
       </c>
       <c r="F6" s="5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Pass</v>
+        <v>First class</v>
       </c>
       <c r="G6" s="21" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -3345,23 +3405,23 @@
       </c>
       <c r="C8" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D8" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>C+</v>
+        <v>D</v>
       </c>
       <c r="E8" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="F8" s="5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="G8" s="21" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="H8">
         <f t="shared" ca="1" si="4"/>
@@ -3438,23 +3498,23 @@
       </c>
       <c r="C10" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="D10" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B+</v>
+        <v>D</v>
       </c>
       <c r="E10" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Disctinction</v>
+        <v>Fail</v>
       </c>
       <c r="F10" s="5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Disctinction</v>
+        <v>Fail</v>
       </c>
       <c r="G10" s="21" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="H10">
         <f t="shared" ca="1" si="4"/>
@@ -3476,11 +3536,11 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D11" s="21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>A+</v>
+        <v>A</v>
       </c>
       <c r="E11" s="5" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -3618,7 +3678,7 @@
       </c>
       <c r="B2" s="6">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C2" s="16">
         <v>1001</v>
@@ -3642,7 +3702,7 @@
       </c>
       <c r="B3" s="2">
         <f t="shared" ref="B3:B11" ca="1" si="1">RANDBETWEEN(1,100)</f>
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C3" s="17">
         <v>1002</v>
@@ -3654,7 +3714,7 @@
       </c>
       <c r="B4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C4" s="17">
         <v>1003</v>
@@ -3669,7 +3729,7 @@
       </c>
       <c r="B5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C5" s="17">
         <v>1004</v>
@@ -3681,7 +3741,7 @@
       </c>
       <c r="B6" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="17">
         <v>1005</v>
@@ -3711,14 +3771,14 @@
       </c>
       <c r="B7" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C7" s="17">
         <v>1006</v>
       </c>
       <c r="E7" s="71">
         <f ca="1">INDEX($A$1:$C$11,$I7,E$2)</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F7" s="71" t="str">
         <f>INDEX($A$1:$C$11,$I7,F$2)</f>
@@ -3733,7 +3793,7 @@
       </c>
       <c r="K7" s="10">
         <f ca="1">INDEX($A$1:$C$11,MATCH($M7,$C$1:$C$11,0),MATCH(K$6,$A$1:$C$1,0))</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L7" s="10" t="str">
         <f>INDEX($A$1:$C$11,MATCH($M7,$C$1:$C$11,0),MATCH(L$6,$A$1:$C$1,0))</f>
@@ -3749,14 +3809,14 @@
       </c>
       <c r="B8" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="C8" s="17">
         <v>1007</v>
       </c>
       <c r="E8" s="71">
         <f t="shared" ref="E8:F16" ca="1" si="2">INDEX($A$1:$C$11,$I8,E$2)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3771,7 +3831,7 @@
       </c>
       <c r="K8" s="10">
         <f t="shared" ref="K8:L16" ca="1" si="4">INDEX($A$1:$C$11,MATCH($M8,$C$1:$C$11,0),MATCH(K$6,$A$1:$C$1,0))</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3787,14 +3847,14 @@
       </c>
       <c r="B9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C9" s="17">
         <v>1008</v>
       </c>
       <c r="E9" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="F9" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3809,7 +3869,7 @@
       </c>
       <c r="K9" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="L9" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3825,14 +3885,14 @@
       </c>
       <c r="B10" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="C10" s="17">
         <v>1009</v>
       </c>
       <c r="E10" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F10" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3847,7 +3907,7 @@
       </c>
       <c r="K10" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="L10" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3863,14 +3923,14 @@
       </c>
       <c r="B11" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C11" s="18">
         <v>1010</v>
       </c>
       <c r="E11" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F11" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3885,7 +3945,7 @@
       </c>
       <c r="K11" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="L11" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3898,7 +3958,7 @@
     <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E12" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="F12" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3913,7 +3973,7 @@
       </c>
       <c r="K12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="L12" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3929,7 +3989,7 @@
       </c>
       <c r="E13" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F13" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3944,7 +4004,7 @@
       </c>
       <c r="K13" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L13" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3957,7 +4017,7 @@
     <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E14" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="F14" s="71" t="str">
         <f t="shared" si="2"/>
@@ -3972,7 +4032,7 @@
       </c>
       <c r="K14" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="L14" s="10" t="str">
         <f t="shared" si="4"/>
@@ -3985,7 +4045,7 @@
     <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E15" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F15" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4000,7 +4060,7 @@
       </c>
       <c r="K15" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="L15" s="10" t="str">
         <f t="shared" si="4"/>
@@ -4016,7 +4076,7 @@
       </c>
       <c r="E16" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F16" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4031,7 +4091,7 @@
       </c>
       <c r="K16" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="L16" s="10" t="str">
         <f t="shared" si="4"/>
@@ -4099,43 +4159,43 @@
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:O2" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H2" s="72">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="J2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="K2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="L2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="M2" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="N2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="O2" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4202,7 +4262,7 @@
     <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="71">
         <f ca="1">INDEX($E$1:$O$3,MATCH(A$6,$E$1:$E$3,0),MATCH($C7,$E$3:$O$3,0))</f>
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B7" s="71" t="str">
         <f>INDEX($E$1:$O$3,MATCH(B$6,$E$1:$E$3,0),MATCH($C7,$E$3:$O$3,0))</f>
@@ -4213,7 +4273,7 @@
       </c>
       <c r="E7" s="73">
         <f ca="1">INDEX($E$1:$O$3,MATCH(E$6,$E$1:$E$3,0),MATCH($G7,$E$3:$O$3,0))</f>
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="F7" s="73" t="str">
         <f>INDEX($E$1:$O$3,MATCH(F$6,$E$1:$E$3,0),MATCH($G7,$E$3:$O$3,0))</f>
@@ -4227,49 +4287,49 @@
       </c>
       <c r="J7" s="10">
         <f ca="1">INDEX($E$1:$O$3,MATCH($I7,$E$1:$E$3,0),MATCH(J$9,$E$3:$O$3,0))</f>
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="K7" s="10">
         <f t="shared" ref="K7:S8" ca="1" si="1">INDEX($E$1:$O$3,MATCH($I7,$E$1:$E$3,0),MATCH(K$9,$E$3:$O$3,0))</f>
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="L7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="M7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="O7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="P7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="Q7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="R7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="71">
         <f t="shared" ref="A8:B16" ca="1" si="2">INDEX($E$1:$O$3,MATCH(A$6,$E$1:$E$3,0),MATCH($C8,$E$3:$O$3,0))</f>
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="B8" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4280,7 +4340,7 @@
       </c>
       <c r="E8" s="73">
         <f t="shared" ref="E8:F16" ca="1" si="3">INDEX($E$1:$O$3,MATCH(E$6,$E$1:$E$3,0),MATCH($G8,$E$3:$O$3,0))</f>
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="F8" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4336,7 +4396,7 @@
     <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="B9" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4347,7 +4407,7 @@
       </c>
       <c r="E9" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="F9" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4393,7 +4453,7 @@
     <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4404,7 +4464,7 @@
       </c>
       <c r="E10" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4417,7 +4477,7 @@
     <row r="11" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B11" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4428,7 +4488,7 @@
       </c>
       <c r="E11" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F11" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4474,7 +4534,7 @@
     <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="B12" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4485,7 +4545,7 @@
       </c>
       <c r="E12" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="F12" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4499,49 +4559,49 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">INDEX($E$1:$O$3,MATCH($I12,$E$1:$E$3,0),MATCH(J$11,$E$3:$O$3,0))</f>
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="K12" s="10">
         <f t="shared" ref="K12:S13" ca="1" si="4">INDEX($E$1:$O$3,MATCH($I12,$E$1:$E$3,0),MATCH(K$11,$E$3:$O$3,0))</f>
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="L12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="O12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="P12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="Q12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="R12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="S12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="B13" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4552,7 +4612,7 @@
       </c>
       <c r="E13" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="F13" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4608,7 +4668,7 @@
     <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B14" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4619,7 +4679,7 @@
       </c>
       <c r="E14" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="F14" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4632,7 +4692,7 @@
     <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="B15" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4643,7 +4703,7 @@
       </c>
       <c r="E15" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F15" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4656,7 +4716,7 @@
     <row r="16" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="71">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B16" s="71" t="str">
         <f t="shared" si="2"/>
@@ -4667,7 +4727,7 @@
       </c>
       <c r="E16" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F16" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4728,42 +4788,42 @@
       </c>
       <c r="D2" s="49">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F2" s="11">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G2" s="27">
         <v>10</v>
       </c>
       <c r="H2" s="1">
         <f t="shared" ref="H2:M2" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="I2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="J2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="K2" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="L2" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4875,39 +4935,39 @@
       </c>
       <c r="H7" s="29">
         <f t="shared" ref="H7:P8" ca="1" si="1">INDEX($C$1:$M$3,MATCH($F7,$C$1:$C$3,0),MATCH(H$6,$C$3:$M$3,0))</f>
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="K7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="L7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="M7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="N7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="O7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="P7" s="29">
         <f t="shared" ca="1" si="1"/>
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4917,7 +4977,7 @@
       </c>
       <c r="C8" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D8" s="17">
         <v>1010</v>
@@ -4973,7 +5033,7 @@
       </c>
       <c r="C9" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D9" s="17">
         <v>1003</v>
@@ -4986,7 +5046,7 @@
       </c>
       <c r="C10" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="D10" s="17">
         <v>1001</v>
@@ -4999,7 +5059,7 @@
       </c>
       <c r="C11" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="D11" s="17">
         <v>1006</v>
@@ -5012,7 +5072,7 @@
       </c>
       <c r="C12" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D12" s="17">
         <v>1002</v>
@@ -5025,7 +5085,7 @@
       </c>
       <c r="C13" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="D13" s="17">
         <v>1005</v>
@@ -5038,7 +5098,7 @@
       </c>
       <c r="C14" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D14" s="17">
         <v>1008</v>
@@ -5051,7 +5111,7 @@
       </c>
       <c r="C15" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D15" s="17">
         <v>1009</v>
@@ -5064,7 +5124,7 @@
       </c>
       <c r="C16" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D16" s="18">
         <v>1007</v>
@@ -5108,7 +5168,7 @@
       </c>
       <c r="B2" s="32">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C2" s="33">
         <v>1001</v>
@@ -5132,7 +5192,7 @@
       </c>
       <c r="B3" s="35">
         <f t="shared" ref="B3:B11" ca="1" si="1">RANDBETWEEN(1,100)</f>
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3" s="36">
         <v>1002</v>
@@ -5144,7 +5204,7 @@
       </c>
       <c r="B4" s="38">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C4" s="36">
         <v>1003</v>
@@ -5159,7 +5219,7 @@
       </c>
       <c r="B5" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C5" s="36">
         <v>1004</v>
@@ -5171,7 +5231,7 @@
       </c>
       <c r="B6" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C6" s="36">
         <v>1005</v>
@@ -5225,7 +5285,7 @@
       </c>
       <c r="B7" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="C7" s="36">
         <v>1006</v>
@@ -5243,7 +5303,7 @@
       </c>
       <c r="H7" s="10">
         <f ca="1">INDEX($A$1:$C$11,MATCH($F7,$C$1:$C$11,0),MATCH(H$6,$A$1:$C$1,0))</f>
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>1</v>
@@ -5295,7 +5355,7 @@
       </c>
       <c r="B8" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="C8" s="36">
         <v>1007</v>
@@ -5313,50 +5373,50 @@
       </c>
       <c r="H8" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>2</v>
       </c>
       <c r="K8" s="10">
         <f ca="1">INDEX($A$1:$C$11,MATCH(K$6,$C$1:$C$11,0),MATCH($J8,$A$1:$C$1,0))</f>
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="L8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="N8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="O8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="R8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="T8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5365,7 +5425,7 @@
       </c>
       <c r="B9" s="39">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C9" s="36">
         <v>1008</v>
@@ -5383,7 +5443,7 @@
       </c>
       <c r="H9" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5392,7 +5452,7 @@
       </c>
       <c r="B10" s="35">
         <f t="shared" ca="1" si="1"/>
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="C10" s="36">
         <v>1009</v>
@@ -5410,7 +5470,7 @@
       </c>
       <c r="H10" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5419,7 +5479,7 @@
       </c>
       <c r="B11" s="41">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C11" s="42">
         <v>1010</v>
@@ -5437,7 +5497,7 @@
       </c>
       <c r="H11" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5454,7 +5514,7 @@
       </c>
       <c r="H12" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5474,7 +5534,7 @@
       </c>
       <c r="H13" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5491,7 +5551,7 @@
       </c>
       <c r="H14" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5508,7 +5568,7 @@
       </c>
       <c r="H15" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5528,7 +5588,7 @@
       </c>
       <c r="H16" s="10">
         <f t="shared" ca="1" si="4"/>
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
